--- a/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>20</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1254</v>
+        <v>1754</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1051</v>
+        <v>1425</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>155</v>
+        <v>275</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,35 +821,35 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>174</v>
+        <v>277</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>209</v>
+        <v>263</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>127</v>
+        <v>194</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>179</v>
+        <v>252</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -910,12 +910,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>09651</t>
+          <t>56391</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA TIRRENA</t>
+          <t>MISTERBIANCO</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -925,39 +925,39 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>116</v>
+        <v>231</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -983,47 +983,47 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
+        <v>156</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>185</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" s="12" t="n">
         <v>107</v>
       </c>
-      <c r="F14" s="12" t="n">
-        <v>141</v>
-      </c>
-      <c r="G14" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="H14" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I14" s="12" t="n">
-        <v>78</v>
-      </c>
       <c r="J14" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>56391</t>
+          <t>09651</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>MISTERBIANCO</t>
+          <t>VILLAFRANCA TIRRENA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,39 +1033,39 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>99</v>
+        <v>151</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1091,28 +1091,28 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>130</v>
+        <v>181</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>0</v>
@@ -1157,23 +1157,23 @@
         <v>0</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>103</v>
+        <v>150</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>1</v>
@@ -1211,16 +1211,16 @@
         <v>0</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
@@ -1234,7 +1234,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>39403</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1253,35 +1253,35 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1307,47 +1307,47 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09627</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,32 +1357,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>64</v>
+        <v>196</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
@@ -1396,12 +1396,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>39403</t>
+          <t>39211</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>SAN GIOVANNI LA PUNTA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,51 +1411,51 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>39211</t>
+          <t>09627</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LA PUNTA</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,32 +1465,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>DIADEMA VITO MANUEL</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>41</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>0</v>
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>15</v>
@@ -1544,14 +1544,14 @@
         <v>0</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1577,28 +1577,28 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>2</v>
@@ -1643,16 +1643,16 @@
         <v>1</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
@@ -1706,68 +1706,64 @@
         <v>0</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>19873</t>
+          <t>09662</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SIRACUSA</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Cali Giuseppe</t>
-        </is>
-      </c>
+          <t>MESSINA</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>LO MONACO GIUSEPPINA</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1789,78 +1785,82 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>09662</t>
+          <t>19873</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr"/>
+          <t>SIRACUSA</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>LO MONACO GIUSEPPINA</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>153</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.1830065359477124</v>
+        <v>28</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>153</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.08496732026143791</v>
+        <v>13</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>109</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.009174311926605505</v>
+        <v>1</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>148</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.006756756756756757</v>
+        <v>1</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>20</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1754</v>
+        <v>1858</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1425</v>
+        <v>1512</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,28 +821,28 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>28</v>
@@ -856,12 +856,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>56553</t>
+          <t>19653</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>MILAZZO</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -871,35 +871,35 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>252</v>
+        <v>204</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>150</v>
+        <v>117</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>28</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>1</v>
@@ -964,12 +964,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>19653</t>
+          <t>56553</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MILAZZO</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -979,39 +979,39 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>185</v>
+        <v>264</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
@@ -1091,28 +1091,28 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>25</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>0</v>
@@ -1157,23 +1157,23 @@
         <v>0</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>1</v>
@@ -1211,16 +1211,16 @@
         <v>0</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
@@ -1253,28 +1253,28 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>22</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>19556</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,51 +1303,51 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>63</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>50</v>
+        <v>212</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>19556</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,39 +1357,39 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>196</v>
+        <v>61</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1415,28 +1415,28 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J22" s="12" t="n">
         <v>22</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>1</v>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>3</v>
@@ -1487,10 +1487,10 @@
         <v>9</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>0</v>
@@ -1535,23 +1535,23 @@
         <v>0</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>1</v>
@@ -1589,16 +1589,16 @@
         <v>1</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
@@ -1634,7 +1634,7 @@
         <v>34</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>2</v>
@@ -1685,22 +1685,22 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="H27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="12" t="n">
-        <v>15</v>
-      </c>
       <c r="J27" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>0</v>
@@ -1735,19 +1735,19 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>5</v>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1785,19 +1785,19 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>4</v>
@@ -1806,7 +1806,7 @@
         <v>1</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>0</v>
@@ -1851,16 +1851,16 @@
         <v>0</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
@@ -1728,7 +1728,11 @@
           <t>MESSINA</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
           <t>MONTISANTI GIUSEPPE</t>
@@ -1778,7 +1782,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
           <t>ARMELLINI GIACOMO</t>

--- a/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>20</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1858</v>
+        <v>1954</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1512</v>
+        <v>1595</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>300</v>
+        <v>327</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,28 +821,28 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>295</v>
+        <v>322</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>28</v>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>250</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>28</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>1</v>
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>99</v>
@@ -995,7 +995,7 @@
         <v>34</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>73</v>
@@ -1004,7 +1004,7 @@
         <v>10</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>13</v>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>39</v>
@@ -1112,7 +1112,7 @@
         <v>25</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>0</v>
@@ -1157,16 +1157,16 @@
         <v>0</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
@@ -1199,28 +1199,28 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>19</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
@@ -1253,19 +1253,19 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>30</v>
@@ -1274,14 +1274,14 @@
         <v>9</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>22</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>0</v>
@@ -1373,16 +1373,16 @@
         <v>0</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
@@ -1415,28 +1415,28 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J22" s="12" t="n">
         <v>22</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>1</v>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>3</v>
@@ -1481,16 +1481,16 @@
         <v>1</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>26</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
@@ -1504,12 +1504,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>59427</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CALATABIANO</t>
+          <t>PATERNÒ</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,32 +1519,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
@@ -1558,12 +1558,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>59427</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>PATERNÒ</t>
+          <t>CALATABIANO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,39 +1573,39 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
         <v>34</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>2</v>
@@ -1666,12 +1666,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09896</t>
+          <t>19873</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CARLENTINI</t>
+          <t>SIRACUSA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,23 +1681,23 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>DIADEMA VITO MANUEL</t>
+          <t>LO MONACO GIUSEPPINA</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J27" s="12" t="n">
         <v>3</v>
@@ -1706,10 +1706,10 @@
         <v>0</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1720,12 +1720,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>09662</t>
+          <t>55106</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,32 +1735,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
@@ -1774,12 +1774,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>55106</t>
+          <t>09662</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,51 +1789,51 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>19873</t>
+          <t>09896</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SIRACUSA</t>
+          <t>CARLENTINI</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,23 +1843,23 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>LO MONACO GIUSEPPINA</t>
+          <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="12" t="n">
         <v>17</v>
-      </c>
-      <c r="F30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="12" t="n">
-        <v>16</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>3</v>
@@ -1868,14 +1868,14 @@
         <v>0</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>20</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1954</v>
+        <v>2082</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1595</v>
+        <v>1706</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>327</v>
+        <v>364</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,28 +821,28 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>322</v>
+        <v>355</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>298</v>
+        <v>357</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>28</v>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>47</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>250</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>28</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>28</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>1</v>
@@ -964,12 +964,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>56553</t>
+          <t>09651</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>VILLAFRANCA TIRRENA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -979,51 +979,51 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>278</v>
+        <v>205</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09651</t>
+          <t>56553</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA TIRRENA</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,39 +1033,39 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>190</v>
+        <v>302</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>39</v>
@@ -1112,7 +1112,7 @@
         <v>25</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>0</v>
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>47</v>
@@ -1166,14 +1166,14 @@
         <v>6</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>1</v>
@@ -1211,16 +1211,16 @@
         <v>1</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
@@ -1234,12 +1234,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>39403</t>
+          <t>19556</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,46 +1249,46 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>226</v>
+        <v>70</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>39403</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>181</v>
+        <v>137</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>19556</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,39 +1357,39 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>66</v>
+        <v>240</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1415,28 +1415,28 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>18</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>1</v>
@@ -1469,19 +1469,19 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>10</v>
@@ -1490,7 +1490,7 @@
         <v>26</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
@@ -1523,28 +1523,28 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>0</v>
@@ -1589,16 +1589,16 @@
         <v>0</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>2</v>
@@ -1643,16 +1643,16 @@
         <v>1</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
@@ -1666,12 +1666,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>19873</t>
+          <t>09662</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SIRACUSA</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,35 +1681,35 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>LO MONACO GIUSEPPINA</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>4</v>
@@ -1760,7 +1760,7 @@
         <v>1</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
@@ -1774,12 +1774,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>09662</t>
+          <t>19873</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>SIRACUSA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,35 +1789,35 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>LO MONACO GIUSEPPINA</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>0</v>
@@ -1859,7 +1859,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>3</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>20</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2082</v>
+        <v>2250</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1706</v>
+        <v>1849</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>364</v>
+        <v>413</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,28 +821,28 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>357</v>
+        <v>389</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>28</v>
@@ -856,12 +856,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>19653</t>
+          <t>56391</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>MILAZZO</t>
+          <t>MISTERBIANCO</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -871,35 +871,35 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -910,12 +910,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>56391</t>
+          <t>19653</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>MISTERBIANCO</t>
+          <t>MILAZZO</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -925,35 +925,35 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>131</v>
+        <v>174</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,28 +983,28 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>99</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>13</v>
@@ -1091,28 +1091,28 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -1145,35 +1145,35 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1199,28 +1199,28 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
@@ -1234,12 +1234,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>19556</t>
+          <t>39403</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,51 +1249,51 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>70</v>
+        <v>248</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>39403</t>
+          <t>19556</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,39 +1303,39 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>238</v>
+        <v>76</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1361,28 +1361,28 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>25</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="J21" s="12" t="n">
         <v>22</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>9</v>
@@ -1427,16 +1427,16 @@
         <v>3</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>1</v>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>3</v>
@@ -1481,16 +1481,16 @@
         <v>2</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>26</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>1</v>
@@ -1535,16 +1535,16 @@
         <v>2</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
@@ -1577,19 +1577,19 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="12" t="n">
         <v>54</v>
-      </c>
-      <c r="F25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>53</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>16</v>
@@ -1598,14 +1598,14 @@
         <v>1</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1631,19 +1631,19 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>17</v>
@@ -1652,7 +1652,7 @@
         <v>4</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
@@ -1685,22 +1685,22 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>0</v>
@@ -1713,19 +1713,19 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>55106</t>
+          <t>19873</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SIRACUSA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>LO MONACO GIUSEPPINA</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>0</v>
@@ -1757,13 +1757,13 @@
         <v>4</v>
       </c>
       <c r="K28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="M28" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="L28" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="M28" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1774,12 +1774,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>19873</t>
+          <t>55106</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SIRACUSA</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,35 +1789,35 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>LO MONACO GIUSEPPINA</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N30" headerRowCount="1">
-  <autoFilter ref="A10:N30"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O30" headerRowCount="1">
+  <autoFilter ref="A10:O30"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>VIA ALCIDE DE GASPERI</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>388</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>389</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>285</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>198</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>VIA CARLO MARX 60</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>208</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>263</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>175</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>141</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -920,42 +946,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>VIALE A. GRAMSCI 156/158</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>GUARISCO ADELINO</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>202</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>258</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>174</v>
       </c>
-      <c r="M13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -974,42 +1005,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>VILLAFRANCA TIRRENA SNC</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>GUARISCO ADELINO</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>222</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>172</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>152</v>
       </c>
-      <c r="M14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1028,42 +1064,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>NAZIONALE 102 PER CATANIA</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>174</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>311</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>99</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>166</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>176</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1082,42 +1123,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>VIA MARCONI</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>151</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>120</v>
       </c>
-      <c r="M16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1136,42 +1182,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>VIA LUIGI STURZO SN</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>119</v>
       </c>
-      <c r="F17" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="12" t="n">
         <v>107</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="M17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1190,42 +1241,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>PROVINCIALE MACCHIA DI GIARRE</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>170</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="I18" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="J18" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="L18" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="M18" s="12" t="n">
         <v>149</v>
       </c>
-      <c r="M18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1244,42 +1300,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>VIALE GIOSTRA ANGOLO VIA ABETONE SNC</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>GUARISCO ADELINO</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>154</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="J19" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="L19" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="M19" s="12" t="n">
         <v>248</v>
       </c>
-      <c r="M19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="N19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1298,42 +1359,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>S .S.114 KM. 79+727 - VIALE DELLO JONIO  21</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="F20" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="H20" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="L20" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="M20" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="M20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1352,42 +1418,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>VIA UMBERTO BONINO, 1</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>GUARISCO ADELINO</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>198</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="I21" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="J21" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="K21" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="L21" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="M21" s="12" t="n">
         <v>263</v>
       </c>
-      <c r="M21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="N21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1406,42 +1477,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>VIA CRISTOFORO COLOMBO, 4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="I22" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="J22" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="K22" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="L22" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="L22" s="12" t="n">
+      <c r="M22" s="12" t="n">
         <v>188</v>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="N22" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1460,42 +1536,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>VIALE KENNEDY</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>176</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="H23" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="I23" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="J23" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="K23" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K23" s="12" t="n">
+      <c r="L23" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="M23" s="12" t="n">
         <v>126</v>
       </c>
-      <c r="M23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="N23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1514,42 +1595,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>USCITA PER SCHETTINO</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="I24" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="J24" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="K24" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="L24" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L24" s="12" t="n">
+      <c r="M24" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="M24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1568,20 +1654,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>C. DA PASTERIA</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="F25" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G25" s="12" t="n">
         <v>0</v>
       </c>
@@ -1589,21 +1677,24 @@
         <v>0</v>
       </c>
       <c r="I25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="K25" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="K25" s="12" t="n">
+      <c r="L25" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L25" s="12" t="n">
+      <c r="M25" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="M25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="N25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1622,42 +1713,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>VIA ACQUICELLA PORTO 5</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>111</v>
-      </c>
-      <c r="G26" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I26" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="K26" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="K26" s="12" t="n">
+      <c r="L26" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L26" s="12" t="n">
+      <c r="M26" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="M26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="N26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1676,42 +1772,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>SS.114 KM. 15+417</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="F27" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H27" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="K27" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K27" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="M27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="N27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1730,42 +1831,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>S.S. 115 KM. 407+254 C/DA PANTANELLI S.N.</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>LO MONACO GIUSEPPINA</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="F28" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="K28" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K28" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="M28" s="12" t="n">
+      <c r="N28" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1784,42 +1890,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>VIA A. DORIA</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="F29" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="H29" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="K29" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K29" s="12" t="n">
+      <c r="L29" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="M29" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="M29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="N29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1838,42 +1949,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>VIA COMUNALE PER CATANIA</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
           <t>Cali Giuseppe</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F30" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H30" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="J30" s="12" t="n">
+      <c r="K30" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K30" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="M30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="N30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>20</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2250</v>
+        <v>2373</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1849</v>
+        <v>1954</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>413</v>
+        <v>458</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>388</v>
+        <v>415</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="K11" s="12" t="n">
+        <v>103</v>
+      </c>
+      <c r="L11" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="L11" s="12" t="n">
-        <v>90</v>
-      </c>
       <c r="M11" s="12" t="n">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>28</v>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>28</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>1</v>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>0</v>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>9</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>0</v>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>13</v>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>0</v>
@@ -1196,35 +1196,35 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>1</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>24</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>0</v>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>0</v>
@@ -1373,35 +1373,35 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L20" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1432,19 +1432,19 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>22</v>
@@ -1453,7 +1453,7 @@
         <v>21</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>9</v>
@@ -1503,16 +1503,16 @@
         <v>3</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>1</v>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>3</v>
@@ -1562,16 +1562,16 @@
         <v>2</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
@@ -1609,28 +1609,28 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>0</v>
@@ -1668,35 +1668,35 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>2</v>
@@ -1739,7 +1739,7 @@
         <v>2</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>17</v>
@@ -1748,7 +1748,7 @@
         <v>4</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>0</v>
@@ -1786,22 +1786,22 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>0</v>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1845,19 +1845,19 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>4</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>1</v>
@@ -1910,7 +1910,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>0</v>
@@ -1925,14 +1925,14 @@
         <v>1</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1984,14 +1984,14 @@
         <v>0</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>20</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2373</v>
+        <v>2485</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1954</v>
+        <v>2051</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>458</v>
+        <v>495</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>428</v>
+        <v>485</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>93</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>28</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>28</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>1</v>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>48</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>0</v>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>9</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>0</v>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>40</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>13</v>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>27</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>0</v>
@@ -1196,35 +1196,35 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K17" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="L17" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="M17" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="L17" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="M17" s="12" t="n">
-        <v>47</v>
-      </c>
       <c r="N17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>4</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>0</v>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>0</v>
@@ -1385,40 +1385,40 @@
         <v>0</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L20" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>39211</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>SAN GIOVANNI LA PUNTA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA UMBERTO BONINO, 1</t>
+          <t>VIA CRISTOFORO COLOMBO, 4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,35 +1428,35 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>210</v>
+        <v>161</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>276</v>
+        <v>204</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1467,17 +1467,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>39211</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LA PUNTA</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA CRISTOFORO COLOMBO, 4</t>
+          <t>VIA UMBERTO BONINO, 1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,35 +1487,35 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>DIADEMA VITO MANUEL</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>154</v>
+        <v>214</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>199</v>
+        <v>293</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
@@ -1609,19 +1609,19 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>13</v>
@@ -1630,14 +1630,14 @@
         <v>3</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>0</v>
@@ -1680,23 +1680,23 @@
         <v>0</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>2</v>
@@ -1739,16 +1739,16 @@
         <v>2</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>0</v>
@@ -1786,35 +1786,35 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1866,14 +1866,14 @@
         <v>0</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1904,19 +1904,19 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>4</v>
@@ -1925,7 +1925,7 @@
         <v>1</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>0</v>
@@ -1963,19 +1963,19 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>3</v>
@@ -1984,7 +1984,7 @@
         <v>0</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>20</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2485</v>
+        <v>2637</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2051</v>
+        <v>2175</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>495</v>
+        <v>542</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>427</v>
+        <v>449</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>485</v>
+        <v>550</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -936,17 +936,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>19653</t>
+          <t>09651</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>MILAZZO</t>
+          <t>VILLAFRANCA TIRRENA</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>VIALE A. GRAMSCI 156/158</t>
+          <t>VILLAFRANCA TIRRENA SNC</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -960,52 +960,52 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09651</t>
+          <t>19653</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA TIRRENA</t>
+          <t>MILAZZO</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA TIRRENA SNC</t>
+          <t>VIALE A. GRAMSCI 156/158</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1019,35 +1019,35 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>240</v>
+        <v>295</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>40</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>13</v>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>0</v>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>0</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>4</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>0</v>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>0</v>
@@ -1385,40 +1385,40 @@
         <v>0</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L20" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>39211</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LA PUNTA</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA CRISTOFORO COLOMBO, 4</t>
+          <t>VIA UMBERTO BONINO, 1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,35 +1428,35 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>DIADEMA VITO MANUEL</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>161</v>
+        <v>231</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>204</v>
+        <v>314</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1467,17 +1467,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>39211</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>SAN GIOVANNI LA PUNTA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA UMBERTO BONINO, 1</t>
+          <t>VIA CRISTOFORO COLOMBO, 4</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,35 +1487,35 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>214</v>
+        <v>183</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>293</v>
+        <v>213</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>59427</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>PATERNÒ</t>
+          <t>CALATABIANO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>USCITA PER SCHETTINO</t>
+          <t>C. DA PASTERIA</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,56 +1605,56 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
         <v>68</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>59427</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CALATABIANO</t>
+          <t>PATERNÒ</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>C. DA PASTERIA</t>
+          <t>USCITA PER SCHETTINO</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,39 +1664,39 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="H25" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I25" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J25" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>48</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>2</v>
@@ -1786,35 +1786,35 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>0</v>
@@ -1857,10 +1857,10 @@
         <v>0</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L28" s="12" t="n">
         <v>0</v>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1904,28 +1904,28 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>0</v>
@@ -1963,19 +1963,19 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="12" t="n">
         <v>21</v>
-      </c>
-      <c r="G30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="I30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="12" t="n">
-        <v>19</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>3</v>
@@ -1984,7 +1984,7 @@
         <v>0</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>20</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2637</v>
+        <v>2799</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2175</v>
+        <v>2327</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>542</v>
+        <v>601</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>550</v>
+        <v>607</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>34</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>2</v>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>0</v>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>49</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>0</v>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>40</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>13</v>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>35</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>0</v>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>0</v>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>1</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>0</v>
@@ -1314,19 +1314,19 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>6</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>42</v>
@@ -1335,7 +1335,7 @@
         <v>14</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>0</v>
@@ -1349,17 +1349,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>19556</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>S .S.114 KM. 79+727 - VIALE DELLO JONIO  21</t>
+          <t>VIA UMBERTO BONINO, 1</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,56 +1369,56 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>39</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>101</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>95</v>
+        <v>329</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>19556</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA UMBERTO BONINO, 1</t>
+          <t>S .S.114 KM. 79+727 - VIALE DELLO JONIO  21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,39 +1428,39 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>314</v>
+        <v>101</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>12</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>27</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>2</v>
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
@@ -1609,28 +1609,28 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>0</v>
@@ -1668,19 +1668,19 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>13</v>
@@ -1689,7 +1689,7 @@
         <v>3</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>0</v>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>2</v>
@@ -1739,16 +1739,16 @@
         <v>2</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>0</v>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="K27" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="L27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="12" t="n">
         <v>22</v>
-      </c>
-      <c r="I27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="K27" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="L27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="12" t="n">
-        <v>20</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>1</v>
@@ -1821,17 +1821,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>19873</t>
+          <t>09896</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SIRACUSA</t>
+          <t>CARLENTINI</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>S.S. 115 KM. 407+254 C/DA PANTANELLI S.N.</t>
+          <t>VIA COMUNALE PER CATANIA</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,23 +1841,23 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>LO MONACO GIUSEPPINA</t>
+          <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>5</v>
@@ -1866,10 +1866,10 @@
         <v>0</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,17 +1880,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>55106</t>
+          <t>19873</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>SIRACUSA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA A. DORIA</t>
+          <t>S.S. 115 KM. 407+254 C/DA PANTANELLI S.N.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,35 +1900,35 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>LO MONACO GIUSEPPINA</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="N29" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="M29" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="N29" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1939,17 +1939,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>09896</t>
+          <t>55106</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CARLENTINI</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIA COMUNALE PER CATANIA</t>
+          <t>VIA A. DORIA</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,39 +1959,39 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>DIADEMA VITO MANUEL</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>20</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2799</v>
+        <v>2960</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2327</v>
+        <v>2465</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>601</v>
+        <v>664</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>463</v>
+        <v>486</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>607</v>
+        <v>656</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>28</v>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>337</v>
+        <v>365</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>2</v>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>0</v>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>36</v>
@@ -1031,16 +1031,16 @@
         <v>7</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>0</v>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>13</v>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>35</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>0</v>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>0</v>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>1</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>0</v>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>228</v>
+        <v>261</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>6</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>0</v>
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>31</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>25</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>329</v>
+        <v>353</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>0</v>
@@ -1444,23 +1444,23 @@
         <v>0</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>2</v>
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>16</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
@@ -1609,35 +1609,35 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>3</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>0</v>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>19554</t>
+          <t>09662</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA ACQUICELLA PORTO 5</t>
+          <t>SS.114 KM. 15+417</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,56 +1723,56 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>154</v>
+        <v>1</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>116</v>
+        <v>25</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09662</t>
+          <t>19554</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>SS.114 KM. 15+417</t>
+          <t>VIA ACQUICELLA PORTO 5</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,56 +1782,56 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>1</v>
+        <v>168</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>09896</t>
+          <t>55106</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CARLENTINI</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA COMUNALE PER CATANIA</t>
+          <t>VIA A. DORIA</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,32 +1841,32 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>DIADEMA VITO MANUEL</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>0</v>
@@ -1916,40 +1916,40 @@
         <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>55106</t>
+          <t>09896</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>CARLENTINI</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIA A. DORIA</t>
+          <t>VIA COMUNALE PER CATANIA</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,32 +1959,32 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>20</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2960</v>
+        <v>3149</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2465</v>
+        <v>2628</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>664</v>
+        <v>745</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>486</v>
+        <v>521</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>656</v>
+        <v>700</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>375</v>
+        <v>405</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>365</v>
+        <v>397</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I12" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>264</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>142</v>
+      </c>
+      <c r="L12" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="J12" s="12" t="n">
-        <v>246</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>133</v>
-      </c>
-      <c r="L12" s="12" t="n">
-        <v>35</v>
-      </c>
       <c r="M12" s="12" t="n">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>2</v>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>0</v>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>54</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>0</v>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>13</v>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>35</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>0</v>
@@ -1196,52 +1196,52 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>55063</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>GIARRE</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>PROVINCIALE MACCHIA DI GIARRE</t>
+          <t>VIA UMBERTO BONINO, 1</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,35 +1251,35 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>209</v>
+        <v>259</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="I18" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <v>125</v>
+      </c>
+      <c r="K18" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="L18" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="M18" s="12" t="n">
+        <v>383</v>
+      </c>
+      <c r="N18" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="J18" s="12" t="n">
-        <v>107</v>
-      </c>
-      <c r="K18" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="L18" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="M18" s="12" t="n">
-        <v>185</v>
-      </c>
-      <c r="N18" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>39403</t>
+          <t>55063</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>GIARRE</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIALE GIOSTRA ANGOLO VIA ABETONE SNC</t>
+          <t>PROVINCIALE MACCHIA DI GIARRE</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,32 +1310,32 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>261</v>
+        <v>218</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>320</v>
+        <v>201</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>0</v>
@@ -1349,7 +1349,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>39403</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA UMBERTO BONINO, 1</t>
+          <t>VIALE GIOSTRA ANGOLO VIA ABETONE SNC</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>0</v>
@@ -1444,16 +1444,16 @@
         <v>0</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>35</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>2</v>
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>16</v>
@@ -1571,7 +1571,7 @@
         <v>41</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
@@ -1609,28 +1609,28 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>0</v>
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>4</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>0</v>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09662</t>
+          <t>19554</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>SS.114 KM. 15+417</t>
+          <t>VIA ACQUICELLA PORTO 5</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,56 +1723,56 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1</v>
+        <v>192</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>25</v>
+        <v>136</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>19554</t>
+          <t>09662</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA ACQUICELLA PORTO 5</t>
+          <t>SS.114 KM. 15+417</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,39 +1782,39 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>168</v>
+        <v>1</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1845,35 +1845,35 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L28" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>0</v>
@@ -1916,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>6</v>
@@ -1925,14 +1925,14 @@
         <v>0</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>20</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3149</v>
+        <v>3347</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2628</v>
+        <v>2787</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>745</v>
+        <v>839</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>521</v>
+        <v>562</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>700</v>
+        <v>752</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>405</v>
+        <v>433</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>397</v>
+        <v>421</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>39</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>2</v>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>13</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>0</v>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>54</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>0</v>
@@ -1054,17 +1054,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>56553</t>
+          <t>09619</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>FIUMEFREDDO DI SICILIA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>NAZIONALE 102 PER CATANIA</t>
+          <t>VIA MARCONI</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>405</v>
+        <v>282</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>272</v>
+        <v>172</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1113,17 +1113,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>09619</t>
+          <t>56553</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>FIUMEFREDDO DI SICILIA</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIA MARCONI</t>
+          <t>NAZIONALE 102 PER CATANIA</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>275</v>
+        <v>415</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>170</v>
+        <v>208</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>157</v>
+        <v>285</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>0</v>
@@ -1231,17 +1231,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>55063</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>GIARRE</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VIA UMBERTO BONINO, 1</t>
+          <t>PROVINCIALE MACCHIA DI GIARRE</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,35 +1251,35 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>383</v>
+        <v>213</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>55063</t>
+          <t>39403</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>GIARRE</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>PROVINCIALE MACCHIA DI GIARRE</t>
+          <t>VIALE GIOSTRA ANGOLO VIA ABETONE SNC</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,32 +1310,32 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>218</v>
+        <v>261</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>201</v>
+        <v>366</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>0</v>
@@ -1349,7 +1349,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>39403</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIALE GIOSTRA ANGOLO VIA ABETONE SNC</t>
+          <t>VIA UMBERTO BONINO, 1</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>343</v>
+        <v>403</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1432,35 +1432,35 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>29</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>2</v>
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>41</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
@@ -1609,35 +1609,35 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>4</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>0</v>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>21</v>
@@ -1748,10 +1748,10 @@
         <v>5</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,35 +1786,35 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1845,35 +1845,35 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>0</v>
@@ -1916,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>6</v>
@@ -1925,7 +1925,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>1</v>
@@ -1963,19 +1963,19 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>5</v>
@@ -1984,7 +1984,7 @@
         <v>0</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - VICECONTE ANTONIO.xlsx
@@ -684,13 +684,13 @@
         <v>20</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3347</v>
+        <v>3301</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2787</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>839</v>
+        <v>832</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>752</v>
+        <v>742</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>129</v>
@@ -854,7 +854,7 @@
         <v>229</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>433</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>148</v>
@@ -863,10 +863,10 @@
         <v>116</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>100</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>284</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>151</v>
@@ -922,10 +922,10 @@
         <v>39</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>275</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>45</v>
@@ -972,7 +972,7 @@
         <v>13</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>84</v>
@@ -981,7 +981,7 @@
         <v>50</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>0</v>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>42</v>
@@ -1031,7 +1031,7 @@
         <v>7</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>67</v>
@@ -1040,31 +1040,31 @@
         <v>54</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09619</t>
+          <t>56553</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>FIUMEFREDDO DI SICILIA</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIA MARCONI</t>
+          <t>NAZIONALE 102 PER CATANIA</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>282</v>
+        <v>409</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>36</v>
+        <v>109</v>
       </c>
       <c r="I15" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="L15" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="J15" s="12" t="n">
-        <v>178</v>
-      </c>
-      <c r="K15" s="12" t="n">
-        <v>72</v>
-      </c>
-      <c r="L15" s="12" t="n">
-        <v>36</v>
-      </c>
       <c r="M15" s="12" t="n">
-        <v>172</v>
+        <v>280</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1113,17 +1113,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>56553</t>
+          <t>09619</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>FIUMEFREDDO DI SICILIA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>NAZIONALE 102 PER CATANIA</t>
+          <t>VIA MARCONI</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>415</v>
+        <v>279</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>285</v>
+        <v>167</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>55058</t>
+          <t>55063</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VIA LUIGI STURZO SN</t>
+          <t>PROVINCIALE MACCHIA DI GIARRE</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1196,42 +1196,42 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>64</v>
+        <v>209</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>55063</t>
+          <t>55058</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>PROVINCIALE MACCHIA DI GIARRE</t>
+          <t>VIA LUIGI STURZO SN</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1258,39 +1258,39 @@
         <v>160</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>223</v>
+        <v>0</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>213</v>
+        <v>64</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>39403</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIALE GIOSTRA ANGOLO VIA ABETONE SNC</t>
+          <t>VIA UMBERTO BONINO, 1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>366</v>
+        <v>397</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>39403</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA UMBERTO BONINO, 1</t>
+          <t>VIALE GIOSTRA ANGOLO VIA ABETONE SNC</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>403</v>
+        <v>353</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1432,19 +1432,19 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>38</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>18</v>
@@ -1503,7 +1503,7 @@
         <v>5</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>38</v>
@@ -1512,7 +1512,7 @@
         <v>29</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>2</v>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>21</v>
@@ -1562,7 +1562,7 @@
         <v>2</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>17</v>
@@ -1571,7 +1571,7 @@
         <v>41</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
@@ -1621,7 +1621,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>36</v>
@@ -1630,7 +1630,7 @@
         <v>1</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>0</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>12</v>
@@ -1680,7 +1680,7 @@
         <v>4</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>18</v>
@@ -1689,7 +1689,7 @@
         <v>6</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>0</v>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>3</v>
@@ -1739,7 +1739,7 @@
         <v>4</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>21</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>1</v>
@@ -1789,16 +1789,16 @@
         <v>68</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>26</v>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>10</v>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>0</v>
@@ -1916,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>6</v>
@@ -1925,7 +1925,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>1</v>
@@ -1963,19 +1963,19 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>5</v>
